--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:02</t>
+    <t xml:space="preserve">2026-09-24 01:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -549,10 +549,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3">
@@ -563,10 +563,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4">
@@ -577,10 +577,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5">
@@ -591,10 +591,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.21</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -605,10 +605,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.31</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7">
@@ -773,10 +773,10 @@
         <v>23</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19">
@@ -787,10 +787,10 @@
         <v>25</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20">
@@ -801,10 +801,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21">
@@ -815,10 +815,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -829,10 +829,10 @@
         <v>28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.31</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -843,10 +843,10 @@
         <v>28</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.22</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24">
@@ -871,10 +871,10 @@
         <v>28</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26">
@@ -888,7 +888,7 @@
         <v>-0.13</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:51</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">plot_regional_correl_matriz_m_movinterna_a_2024_arica_y_parinacota.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2024_arica_y_parinacota.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 20:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
